--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Mistral-7B-Instruct-v0.3/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Mistral-7B-Instruct-v0.3/metrics_default_vs_simple.xlsx
@@ -420,22 +420,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.191304347826087</v>
+        <v>0.1238938053097345</v>
       </c>
       <c r="B2">
-        <v>0.2</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C2">
-        <v>0.2887323943661972</v>
+        <v>0.2253521126760563</v>
       </c>
       <c r="D2">
-        <v>0.8080000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="E2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>17</v>
